--- a/docs/Loudentify_PRD_User_Stories (4).xlsx
+++ b/docs/Loudentify_PRD_User_Stories (4).xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2262" uniqueCount="910">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2264" uniqueCount="912">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -2758,6 +2758,12 @@
   </si>
   <si>
     <t xml:space="preserve">Decision needed on what viewer-hours mean.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exposure and focus lock; white balance; device zoom (the phone's own camera zoom, including lens switching on multi-camera phones; default 1.2x, editable per camera); digital zoom only as a fallback capped at 1.2x when device zoom is unavailable on that phone or lens; moving zoom and pan with durations (2s, 4s, 8s, custom; pan off by default); portrait by default. Aperture is removed. LUTs and background blur are not at launch.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supersedes rows 15 and 16 on digital zoom. 12 Oct 2026: digital fallback capped at 1.2x when device zoom is unavailable (docs/DECISIONS.md 2026-10-12, supersedes "never a digital crop").</t>
   </si>
 </sst>
 </file>
@@ -8368,7 +8374,7 @@
         <v>18</v>
       </c>
       <c r="H128" s="2" t="s">
-        <v>493</v>
+        <v>910</v>
       </c>
       <c r="I128" s="5" t="s">
         <v>306</v>
@@ -8383,7 +8389,7 @@
         <v>494</v>
       </c>
       <c r="M128" s="2" t="s">
-        <v>495</v>
+        <v>911</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
